--- a/output/StructureDefinition-provider-parameters-multi-member-match-bundle-in.xlsx
+++ b/output/StructureDefinition-provider-parameters-multi-member-match-bundle-in.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="252">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:48:28-05:00</t>
+    <t>2026-03-17T22:49:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,10 +513,10 @@
     <t>Only one level of nested parameters is allowed.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle</t>
-  </si>
-  <si>
-    <t>MemberBundle</t>
+    <t>Parameters.parameter:MembersToMatch</t>
+  </si>
+  <si>
+    <t>MembersToMatch</t>
   </si>
   <si>
     <t>Operation Parameter</t>
@@ -525,31 +525,31 @@
     <t>A parameter passed to or received from the operation.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.name</t>
-  </si>
-  <si>
-    <t>Bundle of member elements to match for provider access</t>
-  </si>
-  <si>
-    <t>A bundle containing current member demographics, current coverage information, and provider treatment attestation for a single member.</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part</t>
+    <t>Parameters.parameter:MembersToMatch.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.name</t>
+  </si>
+  <si>
+    <t>Member elements to match for provider access</t>
+  </si>
+  <si>
+    <t>A repeating parameter containing current member demographics, current coverage information, and provider treatment attestation for a single member. The name aligns with the ProviderMemberMatch OperationDefinition.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part</t>
   </si>
   <si>
     <t>3</t>
@@ -561,64 +561,64 @@
     <t>The individual components required for a provider to request access to member data: current patient demographics, current coverage, and provider treatment attestation.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part.id</t>
+    <t>Parameters.parameter:MembersToMatch.part.id</t>
   </si>
   <si>
     <t>Parameters.parameter.part.id</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part.extension</t>
+    <t>Parameters.parameter:MembersToMatch.part.extension</t>
   </si>
   <si>
     <t>Parameters.parameter.part.extension</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part.modifierExtension</t>
+    <t>Parameters.parameter:MembersToMatch.part.modifierExtension</t>
   </si>
   <si>
     <t>Parameters.parameter.part.modifierExtension</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part.name</t>
+    <t>Parameters.parameter:MembersToMatch.part.name</t>
   </si>
   <si>
     <t>Parameters.parameter.part.name</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part.value[x]</t>
+    <t>Parameters.parameter:MembersToMatch.part.value[x]</t>
   </si>
   <si>
     <t>Parameters.parameter.part.value[x]</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part.resource</t>
+    <t>Parameters.parameter:MembersToMatch.part.resource</t>
   </si>
   <si>
     <t>Parameters.parameter.part.resource</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part.part</t>
+    <t>Parameters.parameter:MembersToMatch.part.part</t>
   </si>
   <si>
     <t>Parameters.parameter.part.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:MemberPatient</t>
+    <t>Parameters.parameter:MembersToMatch.part:MemberPatient</t>
   </si>
   <si>
     <t>MemberPatient</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:MemberPatient.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:MemberPatient.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:MemberPatient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:MemberPatient.name</t>
+    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.name</t>
   </si>
   <si>
     <t>Current member demographics</t>
@@ -627,10 +627,10 @@
     <t>Current patient demographic information as known by the provider (from provider's EMR or patient-provided information).</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:MemberPatient.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:MemberPatient.resource</t>
+    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.resource</t>
   </si>
   <si>
     <t xml:space="preserve">SubjectOfCare Client Resident
@@ -650,25 +650,25 @@
     <t>Patient[classCode=PAT]</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:MemberPatient.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch</t>
+    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch</t>
   </si>
   <si>
     <t>CoverageToMatch</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.name</t>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.name</t>
   </si>
   <si>
     <t>Current member coverage</t>
@@ -677,10 +677,10 @@
     <t>The member's current active coverage with the payer (typically from insurance card or eligibility verification).</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.resource</t>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.resource</t>
   </si>
   <si>
     <t xml:space="preserve">Coverage {http://hl7.org/fhir/us/davinci-hrex/StructureDefinition/hrex-coverage}
@@ -699,25 +699,25 @@
     <t>Coverage</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:Consent</t>
-  </si>
-  <si>
-    <t>Consent</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:Consent.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:Consent.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:Consent.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:Consent.name</t>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation</t>
+  </si>
+  <si>
+    <t>TreatmentAttestation</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.name</t>
   </si>
   <si>
     <t>Provider treatment attestation</t>
@@ -726,10 +726,10 @@
     <t>Provider's attestation of an active treatment relationship with the member. This is NOT patient consent for payer-to-payer data exchange, but rather the provider's certification that they have a treatment relationship justifying access to the member's data.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:Consent.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:Consent.resource</t>
+    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.resource</t>
   </si>
   <si>
     <t xml:space="preserve">Consent {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/provider-treatment-relationship-consent}
@@ -751,19 +751,46 @@
     <t>FinancialConsent</t>
   </si>
   <si>
-    <t>Parameters.parameter:MemberBundle.part:Consent.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink</t>
+    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink</t>
   </si>
   <si>
     <t>CoverageToLink</t>
   </si>
   <si>
-    <t>Not used in provider requests</t>
-  </si>
-  <si>
-    <t>CoverageToLink is not used in provider-initiated member match requests as providers are not linking historical coverage to new coverage. This element is only relevant for payer-to-payer member match operations.</t>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.name</t>
+  </si>
+  <si>
+    <t>Optional coverage to link (typically not used)</t>
+  </si>
+  <si>
+    <t>CoverageToLink is typically not used in provider-initiated member match requests as providers are not linking historical coverage to new coverage. This element is only relevant for payer-to-payer member match operations.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.resource</t>
+  </si>
+  <si>
+    <t>Insurance or medical plan or a payment agreement</t>
+  </si>
+  <si>
+    <t>This is the Coverage profile which is used to provide insurance information for scheduling an appointment and/or registering a patient.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.part</t>
   </si>
 </sst>
 </file>
@@ -1085,12 +1112,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL54"/>
+  <dimension ref="A1:AL61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="62.0859375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="66.8828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.64453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.25" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="23.85546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
@@ -6851,7 +6878,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>79</v>
@@ -6863,13 +6890,13 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>241</v>
+        <v>157</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>159</v>
@@ -6940,6 +6967,758 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/output/StructureDefinition-provider-parameters-multi-member-match-bundle-in.xlsx
+++ b/output/StructureDefinition-provider-parameters-multi-member-match-bundle-in.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-provider-parameters-multi-member-match-bundle-in.xlsx
+++ b/output/StructureDefinition-provider-parameters-multi-member-match-bundle-in.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,10 +513,10 @@
     <t>Only one level of nested parameters is allowed.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch</t>
-  </si>
-  <si>
-    <t>MembersToMatch</t>
+    <t>Parameters.parameter:MemberBundle</t>
+  </si>
+  <si>
+    <t>MemberBundle</t>
   </si>
   <si>
     <t>Operation Parameter</t>
@@ -525,16 +525,16 @@
     <t>A parameter passed to or received from the operation.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.name</t>
+    <t>Parameters.parameter:MemberBundle.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.name</t>
   </si>
   <si>
     <t>Member elements to match for provider access</t>
@@ -543,13 +543,13 @@
     <t>A repeating parameter containing current member demographics, current coverage information, and provider treatment attestation for a single member. The name aligns with the ProviderMemberMatch OperationDefinition.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part</t>
+    <t>Parameters.parameter:MemberBundle.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part</t>
   </si>
   <si>
     <t>3</t>
@@ -561,64 +561,64 @@
     <t>The individual components required for a provider to request access to member data: current patient demographics, current coverage, and provider treatment attestation.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part.id</t>
+    <t>Parameters.parameter:MemberBundle.part.id</t>
   </si>
   <si>
     <t>Parameters.parameter.part.id</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part.extension</t>
+    <t>Parameters.parameter:MemberBundle.part.extension</t>
   </si>
   <si>
     <t>Parameters.parameter.part.extension</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part.modifierExtension</t>
+    <t>Parameters.parameter:MemberBundle.part.modifierExtension</t>
   </si>
   <si>
     <t>Parameters.parameter.part.modifierExtension</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part.name</t>
+    <t>Parameters.parameter:MemberBundle.part.name</t>
   </si>
   <si>
     <t>Parameters.parameter.part.name</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part.value[x]</t>
+    <t>Parameters.parameter:MemberBundle.part.value[x]</t>
   </si>
   <si>
     <t>Parameters.parameter.part.value[x]</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part.resource</t>
+    <t>Parameters.parameter:MemberBundle.part.resource</t>
   </si>
   <si>
     <t>Parameters.parameter.part.resource</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part.part</t>
+    <t>Parameters.parameter:MemberBundle.part.part</t>
   </si>
   <si>
     <t>Parameters.parameter.part.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:MemberPatient</t>
+    <t>Parameters.parameter:MemberBundle.part:MemberPatient</t>
   </si>
   <si>
     <t>MemberPatient</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.name</t>
+    <t>Parameters.parameter:MemberBundle.part:MemberPatient.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:MemberPatient.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:MemberPatient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:MemberPatient.name</t>
   </si>
   <si>
     <t>Current member demographics</t>
@@ -627,10 +627,10 @@
     <t>Current patient demographic information as known by the provider (from provider's EMR or patient-provided information).</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.resource</t>
+    <t>Parameters.parameter:MemberBundle.part:MemberPatient.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:MemberPatient.resource</t>
   </si>
   <si>
     <t xml:space="preserve">SubjectOfCare Client Resident
@@ -650,25 +650,25 @@
     <t>Patient[classCode=PAT]</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:MemberPatient.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch</t>
+    <t>Parameters.parameter:MemberBundle.part:MemberPatient.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch</t>
   </si>
   <si>
     <t>CoverageToMatch</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.name</t>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.name</t>
   </si>
   <si>
     <t>Current member coverage</t>
@@ -677,10 +677,10 @@
     <t>The member's current active coverage with the payer (typically from insurance card or eligibility verification).</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.resource</t>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.resource</t>
   </si>
   <si>
     <t xml:space="preserve">Coverage {http://hl7.org/fhir/us/davinci-hrex/StructureDefinition/hrex-coverage}
@@ -699,25 +699,25 @@
     <t>Coverage</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToMatch.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation</t>
-  </si>
-  <si>
-    <t>TreatmentAttestation</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.name</t>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToMatch.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:Consent</t>
+  </si>
+  <si>
+    <t>Consent</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:Consent.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:Consent.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:Consent.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:Consent.name</t>
   </si>
   <si>
     <t>Provider treatment attestation</t>
@@ -726,10 +726,10 @@
     <t>Provider's attestation of an active treatment relationship with the member. This is NOT patient consent for payer-to-payer data exchange, but rather the provider's certification that they have a treatment relationship justifying access to the member's data.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.resource</t>
+    <t>Parameters.parameter:MemberBundle.part:Consent.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:Consent.resource</t>
   </si>
   <si>
     <t xml:space="preserve">Consent {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/provider-treatment-relationship-consent}
@@ -751,25 +751,25 @@
     <t>FinancialConsent</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:TreatmentAttestation.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink</t>
+    <t>Parameters.parameter:MemberBundle.part:Consent.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToLink</t>
   </si>
   <si>
     <t>CoverageToLink</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.name</t>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.name</t>
   </si>
   <si>
     <t>Optional coverage to link (typically not used)</t>
@@ -778,10 +778,10 @@
     <t>CoverageToLink is typically not used in provider-initiated member match requests as providers are not linking historical coverage to new coverage. This element is only relevant for payer-to-payer member match operations.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.resource</t>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.resource</t>
   </si>
   <si>
     <t>Insurance or medical plan or a payment agreement</t>
@@ -790,7 +790,7 @@
     <t>This is the Coverage profile which is used to provide insurance information for scheduling an appointment and/or registering a patient.</t>
   </si>
   <si>
-    <t>Parameters.parameter:MembersToMatch.part:CoverageToLink.part</t>
+    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.part</t>
   </si>
 </sst>
 </file>
@@ -1115,9 +1115,9 @@
   <dimension ref="A1:AL61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="66.8828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="62.0859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="35.890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.25" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="23.85546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>

--- a/output/StructureDefinition-provider-parameters-multi-member-match-bundle-in.xlsx
+++ b/output/StructureDefinition-provider-parameters-multi-member-match-bundle-in.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="239">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -752,45 +752,6 @@
   </si>
   <si>
     <t>Parameters.parameter:MemberBundle.part:Consent.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink</t>
-  </si>
-  <si>
-    <t>CoverageToLink</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.name</t>
-  </si>
-  <si>
-    <t>Optional coverage to link (typically not used)</t>
-  </si>
-  <si>
-    <t>CoverageToLink is typically not used in provider-initiated member match requests as providers are not linking historical coverage to new coverage. This element is only relevant for payer-to-payer member match operations.</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.resource</t>
-  </si>
-  <si>
-    <t>Insurance or medical plan or a payment agreement</t>
-  </si>
-  <si>
-    <t>This is the Coverage profile which is used to provide insurance information for scheduling an appointment and/or registering a patient.</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:MemberBundle.part:CoverageToLink.part</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1073,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL61"/>
+  <dimension ref="A1:AL53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.0859375" customWidth="true" bestFit="true"/>
@@ -6860,868 +6821,6 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
